--- a/artfynd/A 28144-2022 artfynd.xlsx
+++ b/artfynd/A 28144-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123646217</v>
       </c>
       <c r="B2" t="n">
-        <v>57361</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28144-2022 artfynd.xlsx
+++ b/artfynd/A 28144-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123646217</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28144-2022 artfynd.xlsx
+++ b/artfynd/A 28144-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123646217</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
